--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702678</v>
+        <v>113702671</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>56029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317431</v>
+        <v>317437</v>
       </c>
       <c r="R2" t="n">
-        <v>6516584</v>
+        <v>6516597</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702737</v>
+        <v>113702678</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +793,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317803</v>
+        <v>317431</v>
       </c>
       <c r="R3" t="n">
-        <v>6516596</v>
+        <v>6516584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702671</v>
+        <v>113702674</v>
       </c>
       <c r="B4" t="n">
-        <v>56029</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,41 +904,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317437</v>
+        <v>317640</v>
       </c>
       <c r="R4" t="n">
-        <v>6516597</v>
+        <v>6516620</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702674</v>
+        <v>113702737</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,43 +1015,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317640</v>
+        <v>317803</v>
       </c>
       <c r="R5" t="n">
-        <v>6516620</v>
+        <v>6516596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702671</v>
+        <v>113702674</v>
       </c>
       <c r="B2" t="n">
-        <v>56029</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317437</v>
+        <v>317640</v>
       </c>
       <c r="R2" t="n">
-        <v>6516597</v>
+        <v>6516620</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702678</v>
+        <v>113702680</v>
       </c>
       <c r="B3" t="n">
         <v>56826</v>
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317431</v>
+        <v>317691</v>
       </c>
       <c r="R3" t="n">
-        <v>6516584</v>
+        <v>6516617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702674</v>
+        <v>113702737</v>
       </c>
       <c r="B4" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,43 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317640</v>
+        <v>317803</v>
       </c>
       <c r="R4" t="n">
-        <v>6516620</v>
+        <v>6516596</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702737</v>
+        <v>113702671</v>
       </c>
       <c r="B5" t="n">
-        <v>96361</v>
+        <v>56029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317803</v>
+        <v>317437</v>
       </c>
       <c r="R5" t="n">
-        <v>6516596</v>
+        <v>6516597</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702680</v>
+        <v>113702678</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317691</v>
+        <v>317431</v>
       </c>
       <c r="R6" t="n">
-        <v>6516617</v>
+        <v>6516584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702680</v>
+        <v>113702671</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317691</v>
+        <v>317437</v>
       </c>
       <c r="R3" t="n">
-        <v>6516617</v>
+        <v>6516597</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702737</v>
+        <v>113702678</v>
       </c>
       <c r="B4" t="n">
-        <v>96365</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +904,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317803</v>
+        <v>317431</v>
       </c>
       <c r="R4" t="n">
-        <v>6516596</v>
+        <v>6516584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702671</v>
+        <v>113702680</v>
       </c>
       <c r="B5" t="n">
-        <v>56029</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,41 +1015,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317437</v>
+        <v>317691</v>
       </c>
       <c r="R5" t="n">
-        <v>6516597</v>
+        <v>6516617</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702678</v>
+        <v>113702737</v>
       </c>
       <c r="B6" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,43 +1126,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317431</v>
+        <v>317803</v>
       </c>
       <c r="R6" t="n">
-        <v>6516584</v>
+        <v>6516596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702674</v>
+        <v>113702737</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317640</v>
+        <v>317803</v>
       </c>
       <c r="R2" t="n">
-        <v>6516620</v>
+        <v>6516596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702737</v>
+        <v>113702674</v>
       </c>
       <c r="B6" t="n">
-        <v>96365</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,38 +1121,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317803</v>
+        <v>317640</v>
       </c>
       <c r="R6" t="n">
-        <v>6516596</v>
+        <v>6516620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702737</v>
+        <v>113702671</v>
       </c>
       <c r="B2" t="n">
-        <v>96365</v>
+        <v>56029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317803</v>
+        <v>317437</v>
       </c>
       <c r="R2" t="n">
-        <v>6516596</v>
+        <v>6516597</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702671</v>
+        <v>113702678</v>
       </c>
       <c r="B3" t="n">
-        <v>56029</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +793,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317437</v>
+        <v>317431</v>
       </c>
       <c r="R3" t="n">
-        <v>6516597</v>
+        <v>6516584</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702678</v>
+        <v>113702680</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317431</v>
+        <v>317691</v>
       </c>
       <c r="R4" t="n">
-        <v>6516584</v>
+        <v>6516617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702680</v>
+        <v>113702737</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,43 +1015,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317691</v>
+        <v>317803</v>
       </c>
       <c r="R5" t="n">
-        <v>6516617</v>
+        <v>6516596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702671</v>
+        <v>113702680</v>
       </c>
       <c r="B2" t="n">
-        <v>56029</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317437</v>
+        <v>317691</v>
       </c>
       <c r="R2" t="n">
-        <v>6516597</v>
+        <v>6516617</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702678</v>
+        <v>113702737</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snaben, Västra Götaland, Dls</t>
+          <t>Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317431</v>
+        <v>317803</v>
       </c>
       <c r="R3" t="n">
-        <v>6516584</v>
+        <v>6516596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702680</v>
+        <v>113702674</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317691</v>
+        <v>317640</v>
       </c>
       <c r="R4" t="n">
-        <v>6516617</v>
+        <v>6516620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113702737</v>
+        <v>113702671</v>
       </c>
       <c r="B5" t="n">
-        <v>96365</v>
+        <v>56029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317803</v>
+        <v>317437</v>
       </c>
       <c r="R5" t="n">
-        <v>6516596</v>
+        <v>6516597</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702674</v>
+        <v>113702678</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317640</v>
+        <v>317431</v>
       </c>
       <c r="R6" t="n">
-        <v>6516620</v>
+        <v>6516584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>130184431</v>
       </c>
       <c r="B7" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>130184431</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>130184431</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>130184431</v>
       </c>
       <c r="B7" t="n">
-        <v>57044</v>
+        <v>57053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702678</v>
+        <v>113702674</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317431</v>
+        <v>317640</v>
       </c>
       <c r="R2" t="n">
-        <v>6516584</v>
+        <v>6516620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702671</v>
+        <v>113702678</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +792,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317437</v>
+        <v>317431</v>
       </c>
       <c r="R3" t="n">
-        <v>6516597</v>
+        <v>6516584</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,19 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702674</v>
+        <v>113702679</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -937,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317640</v>
+        <v>317518</v>
       </c>
       <c r="R4" t="n">
-        <v>6516620</v>
+        <v>6516621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,16 +996,11 @@
         <v>113702680</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702737</v>
+        <v>113702671</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,37 +1110,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lerdal, Västra Götaland, Dls</t>
+          <t>Snaben, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317803</v>
+        <v>317437</v>
       </c>
       <c r="R6" t="n">
-        <v>6516596</v>
+        <v>6516597</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1203,7 @@
         <v>130184431</v>
       </c>
       <c r="B7" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,6 +1304,107 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113702737</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lerdal, Västra Götaland, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>317803</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6516596</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1171-2023 artfynd.xlsx
+++ b/artfynd/A 1171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702680</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702671</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184431</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,8 +1440,22 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>